--- a/results/Int Task Remove ACC -0.8/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_4_permute.xlsx
@@ -440,517 +440,517 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7266088292279049</v>
+        <v>0.7243729432580893</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7214182045387365</v>
+        <v>0.7314705853510244</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7223918516245897</v>
+        <v>0.7349258066911269</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7205459498382625</v>
+        <v>0.719216116030714</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7175574136571166</v>
+        <v>0.7217743912604317</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7172779279108896</v>
+        <v>0.7187767490274036</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7172441304490965</v>
+        <v>0.7167527538802287</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7100048192028423</v>
+        <v>0.7175392015533524</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7105637906952962</v>
+        <v>0.7178433787094903</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7098449379457588</v>
+        <v>0.7184699451255304</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.710529993233503</v>
+        <v>0.7184699451255304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7047401202839407</v>
+        <v>0.7174287031160909</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7044606345377138</v>
+        <v>0.71659024587741</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7044606345377138</v>
+        <v>0.722508829367998</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7080666310830178</v>
+        <v>0.7093821053472138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7007844163230883</v>
+        <v>0.7055213144655939</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6992855952065743</v>
+        <v>0.697815318060383</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6992855952065743</v>
+        <v>0.700220191339164</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6978231982975887</v>
+        <v>0.6992868210212507</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6918955087551186</v>
+        <v>0.6947786248740913</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6889043458282375</v>
+        <v>0.677379061124023</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6881334835131429</v>
+        <v>0.6758464425457158</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.684017898295207</v>
+        <v>0.682673704944306</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.681687099246159</v>
+        <v>0.6817338553202459</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6732557707852639</v>
+        <v>0.6841049311372338</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6746220288003406</v>
+        <v>0.6871025733702618</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6763327407394955</v>
+        <v>0.674605042511253</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6763327407394955</v>
+        <v>0.6747493384103075</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6711850195640022</v>
+        <v>0.6744360552022874</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6728528279894819</v>
+        <v>0.6842739184461994</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.662431301843205</v>
+        <v>0.67999845197118</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6608986832648979</v>
+        <v>0.6744425345084343</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.69415345938911</v>
+        <v>0.6751704933098537</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6870675500937924</v>
+        <v>0.6885441314297482</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6817937451230087</v>
+        <v>0.6757021466466614</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6438838502068475</v>
+        <v>0.67765854687025</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6159925386411809</v>
+        <v>0.67765854687025</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5978403246797822</v>
+        <v>0.6791144644730889</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.585275198897187</v>
+        <v>0.6492082638121295</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.585275198897187</v>
+        <v>0.6467357956097622</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5849281182273739</v>
+        <v>0.6485816973960894</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5766358321740629</v>
+        <v>0.6560420055168665</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6138527915652743</v>
+        <v>0.6563552887248865</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5996198573571996</v>
+        <v>0.6316644041630067</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5976972545954041</v>
+        <v>0.5992701499416512</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5992207671218291</v>
+        <v>0.5806953801496475</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.59830560890768</v>
+        <v>0.5513313398084367</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.603072451951567</v>
+        <v>0.5539974867296805</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5959345330906921</v>
+        <v>0.5405354148367005</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5955627610109679</v>
+        <v>0.5405354148367005</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5747132294122674</v>
+        <v>0.5369996399607179</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.577944827132112</v>
+        <v>0.5431859763999154</v>
       </c>
     </row>
     <row r="54">
@@ -960,367 +960,367 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.592847231269902</v>
+        <v>0.5442636426168832</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5952859020104762</v>
+        <v>0.5459197182447455</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5952859020104762</v>
+        <v>0.5249973382309883</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5407954626644869</v>
+        <v>0.5305324168442347</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5382307081286223</v>
+        <v>0.5711370026519625</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5633777708665179</v>
+        <v>0.5705104362359225</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5590086171269426</v>
+        <v>0.580851233729937</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5662088774199333</v>
+        <v>0.5753758698030711</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5751497945534603</v>
+        <v>0.5771021671002547</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5125894669597415</v>
+        <v>0.5803349906347759</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5123542856582485</v>
+        <v>0.5540412658252675</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5123542856582485</v>
+        <v>0.5446986317106349</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5202357486785718</v>
+        <v>0.5402788693365611</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5724018682816601</v>
+        <v>0.5189962749243147</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.555721157281129</v>
+        <v>0.528457112597032</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5759584820071419</v>
+        <v>0.5114916623588037</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.577546962711418</v>
+        <v>0.4982880622461688</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5446730647188122</v>
+        <v>0.4868070819866883</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5399491251886004</v>
+        <v>0.497604232773101</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.546209535857531</v>
+        <v>0.4992382437367874</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.551547083191489</v>
+        <v>0.4989249605287674</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5532940442217897</v>
+        <v>0.4998648101528275</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5561459896247045</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5553166384379058</v>
+        <v>0.4990601503759399</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5634439648590452</v>
+        <v>0.4993734335839599</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5690947954010235</v>
+        <v>0.5008046597768877</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5602123671392008</v>
+        <v>0.5002456882844338</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5651273586425538</v>
+        <v>0.5032862340311371</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.570640197475242</v>
+        <v>0.5032862340311371</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5460452766908888</v>
+        <v>0.503252436569344</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5606214390083649</v>
+        <v>0.5024139793306632</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5235731166933544</v>
+        <v>0.5024139793306632</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5520832895542378</v>
+        <v>0.5010165505995284</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5386121116093756</v>
+        <v>0.5012622388839623</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.538946233666895</v>
+        <v>0.5002118908226407</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5384900554908792</v>
+        <v>0.5011270490367898</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4985118609828092</v>
+        <v>0.5001104984372614</v>
       </c>
     </row>
   </sheetData>
